--- a/01_analyses_states/Himachal Pradesh/results/SoIB_summaries.xlsx
+++ b/01_analyses_states/Himachal Pradesh/results/SoIB_summaries.xlsx
@@ -588,10 +588,10 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="C7">
-        <v>53</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -599,10 +599,10 @@
         <v>11</v>
       </c>
       <c r="B8">
-        <v>461</v>
+        <v>476</v>
       </c>
       <c r="C8">
-        <v>433</v>
+        <v>466</v>
       </c>
     </row>
   </sheetData>
@@ -697,7 +697,7 @@
         <v>23</v>
       </c>
       <c r="B2">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -705,7 +705,7 @@
         <v>18</v>
       </c>
       <c r="B3">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -713,7 +713,7 @@
         <v>24</v>
       </c>
       <c r="B4">
-        <v>433</v>
+        <v>439</v>
       </c>
     </row>
   </sheetData>
@@ -742,7 +742,7 @@
         <v>28</v>
       </c>
       <c r="B2">
-        <v>499</v>
+        <v>507</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -750,7 +750,7 @@
         <v>29</v>
       </c>
       <c r="B3">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="C3">
         <v>6</v>
@@ -761,7 +761,7 @@
         <v>30</v>
       </c>
       <c r="B4">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="C4">
         <v>13</v>
@@ -807,16 +807,16 @@
         <v>37</v>
       </c>
       <c r="B2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C2">
-        <v>69.8</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="D2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E2">
-        <v>74.7</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -827,13 +827,13 @@
         <v>32</v>
       </c>
       <c r="C3">
-        <v>30.2</v>
+        <v>29.9</v>
       </c>
       <c r="D3">
         <v>25</v>
       </c>
       <c r="E3">
-        <v>25.3</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
